--- a/Department_BillableData.xlsx
+++ b/Department_BillableData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="31">
   <si>
     <t>Billable Type</t>
   </si>
@@ -20,30 +20,30 @@
     <t>Count of Employees</t>
   </si>
   <si>
-    <t>AAAAAAAAAAAA</t>
+    <t>ABCOE</t>
+  </si>
+  <si>
+    <t>InternalRNDProducts</t>
+  </si>
+  <si>
+    <t>Accounts</t>
+  </si>
+  <si>
+    <t>TNM</t>
+  </si>
+  <si>
+    <t>Admin</t>
+  </si>
+  <si>
+    <t>APM</t>
+  </si>
+  <si>
+    <t>Bench</t>
   </si>
   <si>
     <t>Fixed Cost</t>
   </si>
   <si>
-    <t>Accountss</t>
-  </si>
-  <si>
-    <t>Bench</t>
-  </si>
-  <si>
-    <t>InternalRNDProducts</t>
-  </si>
-  <si>
-    <t>TNM</t>
-  </si>
-  <si>
-    <t>Admin</t>
-  </si>
-  <si>
-    <t>APM</t>
-  </si>
-  <si>
     <t>Shadow</t>
   </si>
   <si>
@@ -56,12 +56,18 @@
     <t>Business Development</t>
   </si>
   <si>
+    <t>CEO Office</t>
+  </si>
+  <si>
     <t>Development</t>
   </si>
   <si>
     <t>Director</t>
   </si>
   <si>
+    <t>Floor Automation</t>
+  </si>
+  <si>
     <t>Functional Testing</t>
   </si>
   <si>
@@ -69,6 +75,9 @@
   </si>
   <si>
     <t>IT</t>
+  </si>
+  <si>
+    <t>Legal</t>
   </si>
   <si>
     <t>Performance Testing</t>
@@ -180,11 +189,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C100"/>
+  <dimension ref="A1:C87"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="20.1875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.74609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="19.0859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -205,7 +214,7 @@
         <v>3</v>
       </c>
       <c r="B3" t="n">
-        <v>5.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="4">
@@ -215,84 +224,81 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="2">
         <v>6</v>
-      </c>
-      <c r="B7" t="n">
-        <v>12.0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B8" t="n">
-        <v>1.0</v>
+        <v>17.0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>1.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>2.0</v>
+        <v>31.0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B12" t="n">
-        <v>9.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B13" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="s" s="2">
-        <v>9</v>
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" t="n">
+        <v>53.0</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" t="n">
-        <v>12.0</v>
+      <c r="A15" t="s" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
@@ -300,87 +306,86 @@
         <v>3</v>
       </c>
       <c r="B16" t="n">
-        <v>27.0</v>
+        <v>66.0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B17" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="n">
-        <v>3.0</v>
+      <c r="A18" t="s" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B19" t="n">
-        <v>32.0</v>
+        <v>19.0</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>11</v>
+      <c r="A20" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" t="n">
+        <v>28.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B21" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="B22" t="n">
-        <v>53.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="n">
-        <v>1.0</v>
+        <v>48.0</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="s">
-        <v>7</v>
-      </c>
-      <c r="B24" t="n">
-        <v>8.0</v>
+      <c r="A24" t="s" s="2">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="s" s="2">
-        <v>12</v>
+      <c r="A25" t="s">
+        <v>8</v>
+      </c>
+      <c r="B25" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26"/>
+      <c r="A26" t="s">
+        <v>3</v>
+      </c>
       <c r="B26" t="n">
-        <v>1.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s">
-        <v>5</v>
-      </c>
-      <c r="B27" t="n">
-        <v>11.0</v>
+      <c r="A27" t="s" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -388,34 +393,36 @@
         <v>3</v>
       </c>
       <c r="B28" t="n">
-        <v>55.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s">
-        <v>10</v>
-      </c>
-      <c r="B29" t="n">
-        <v>1.0</v>
+      <c r="A29" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B30" t="n">
-        <v>25.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s" s="2">
-        <v>13</v>
+      <c r="A31" t="s">
+        <v>9</v>
+      </c>
+      <c r="B31" t="n">
+        <v>20.0</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32"/>
+      <c r="A32" t="s">
+        <v>3</v>
+      </c>
       <c r="B32" t="n">
-        <v>2.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="33">
@@ -423,168 +430,160 @@
         <v>5</v>
       </c>
       <c r="B33" t="n">
-        <v>14.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s">
-        <v>3</v>
-      </c>
-      <c r="B34" t="n">
-        <v>2.0</v>
+      <c r="A34" t="s" s="2">
+        <v>16</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B35" t="n">
-        <v>9.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B37" t="n">
-        <v>35.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s">
-        <v>3</v>
-      </c>
-      <c r="B38" t="n">
-        <v>40.0</v>
+      <c r="A38" t="s" s="2">
+        <v>18</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B39" t="n">
-        <v>2.0</v>
+        <v>76.0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B40" t="n">
-        <v>1.0</v>
+        <v>54.0</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B41" t="n">
-        <v>50.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>15</v>
+      <c r="A42" t="s">
+        <v>10</v>
+      </c>
+      <c r="B42" t="n">
+        <v>17.0</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B43" t="n">
-        <v>2.0</v>
+        <v>458.0</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s">
-        <v>6</v>
-      </c>
-      <c r="B44" t="n">
-        <v>4.0</v>
+      <c r="A44" t="s" s="2">
+        <v>19</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>16</v>
+      <c r="A45"/>
+      <c r="B45" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B46" t="n">
-        <v>90.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="s">
-        <v>3</v>
-      </c>
-      <c r="B47" t="n">
-        <v>67.0</v>
+      <c r="A47" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B48" t="n">
-        <v>11.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s">
-        <v>10</v>
-      </c>
-      <c r="B49" t="n">
-        <v>13.0</v>
+      <c r="A49" t="s" s="2">
+        <v>21</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B50" t="n">
-        <v>339.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B52" t="n">
-        <v>8.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B53" t="n">
-        <v>7.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B54" t="n">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s" s="2">
-        <v>18</v>
+      <c r="A55" t="s">
+        <v>10</v>
+      </c>
+      <c r="B55" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="56">
@@ -592,20 +591,17 @@
         <v>5</v>
       </c>
       <c r="B56" t="n">
-        <v>8.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s">
-        <v>3</v>
-      </c>
-      <c r="B57" t="n">
-        <v>2.0</v>
+      <c r="A57" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B58" t="n">
         <v>2.0</v>
@@ -613,63 +609,65 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B59" t="n">
-        <v>2.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B61" t="n">
-        <v>1.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B62" t="n">
-        <v>27.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B63" t="n">
-        <v>22.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s" s="2">
-        <v>20</v>
+      <c r="A64" t="s">
+        <v>10</v>
+      </c>
+      <c r="B64" t="n">
+        <v>3.0</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65"/>
+      <c r="A65" t="s">
+        <v>5</v>
+      </c>
       <c r="B65" t="n">
-        <v>1.0</v>
+        <v>84.0</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="s">
-        <v>5</v>
-      </c>
-      <c r="B66" t="n">
-        <v>9.0</v>
+      <c r="A66" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B67" t="n">
         <v>5.0</v>
@@ -677,68 +675,68 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B68" t="n">
-        <v>1.0</v>
+        <v>65.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B69" t="n">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B71" t="n">
-        <v>10.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s">
-        <v>3</v>
-      </c>
-      <c r="B72" t="n">
-        <v>21.0</v>
+      <c r="A72" t="s" s="2">
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B73" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B74" t="n">
-        <v>1.0</v>
+        <v>23.0</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B75" t="n">
-        <v>47.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="2">
-        <v>22</v>
+      <c r="A76" t="s">
+        <v>10</v>
+      </c>
+      <c r="B76" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="77">
@@ -746,201 +744,104 @@
         <v>5</v>
       </c>
       <c r="B77" t="n">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s">
-        <v>3</v>
-      </c>
-      <c r="B78" t="n">
-        <v>31.0</v>
+      <c r="A78" t="s" s="2">
+        <v>28</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B79" t="n">
-        <v>10.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B80" t="n">
-        <v>3.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="s" s="2">
-        <v>23</v>
+      <c r="A81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="n">
+        <v>2.0</v>
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="s">
-        <v>5</v>
-      </c>
-      <c r="B82" t="n">
-        <v>4.0</v>
+      <c r="A82" t="s" s="2">
+        <v>29</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="s">
-        <v>6</v>
-      </c>
+      <c r="A83"/>
       <c r="B83" t="n">
-        <v>1.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="s" s="2">
-        <v>24</v>
+      <c r="A84" t="s">
+        <v>9</v>
+      </c>
+      <c r="B84" t="n">
+        <v>1.0</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B85" t="n">
         <v>2.0</v>
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="s">
-        <v>3</v>
-      </c>
-      <c r="B86" t="n">
-        <v>8.0</v>
+      <c r="A86" t="s" s="2">
+        <v>30</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B87" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="s">
-        <v>10</v>
-      </c>
-      <c r="B88" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="s">
-        <v>7</v>
-      </c>
-      <c r="B89" t="n">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="s" s="2">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s">
-        <v>5</v>
-      </c>
-      <c r="B91" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="s">
-        <v>7</v>
-      </c>
-      <c r="B92" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="s" s="2">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="s">
-        <v>5</v>
-      </c>
-      <c r="B94" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="s">
-        <v>3</v>
-      </c>
-      <c r="B95" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="s">
-        <v>6</v>
-      </c>
-      <c r="B96" t="n">
-        <v>7.0</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="s" s="2">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="s">
-        <v>5</v>
-      </c>
-      <c r="B98" t="n">
-        <v>59.0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="s">
-        <v>3</v>
-      </c>
-      <c r="B99" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="s">
-        <v>7</v>
-      </c>
-      <c r="B100" t="n">
-        <v>1.0</v>
+        <v>35.0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A7:B7"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="A25:B25"/>
-    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A15:B15"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="A29:B29"/>
+    <mergeCell ref="A34:B34"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A42:B42"/>
-    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A47:B47"/>
+    <mergeCell ref="A49:B49"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A57:B57"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A66:B66"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A84:B84"/>
-    <mergeCell ref="A90:B90"/>
-    <mergeCell ref="A93:B93"/>
-    <mergeCell ref="A97:B97"/>
+    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A82:B82"/>
+    <mergeCell ref="A86:B86"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>

--- a/Department_BillableData.xlsx
+++ b/Department_BillableData.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="30">
   <si>
     <t>Billable Type</t>
   </si>
@@ -42,9 +42,6 @@
   </si>
   <si>
     <t>Fixed Cost</t>
-  </si>
-  <si>
-    <t>Shadow</t>
   </si>
   <si>
     <t>Application Performance Monitoring</t>
@@ -189,7 +186,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C87"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.328125" customWidth="true" bestFit="true"/>
@@ -261,7 +258,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>21.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="11">
@@ -282,84 +279,81 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" t="n">
+        <v>53.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
         <v>10</v>
       </c>
-      <c r="B13" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
-        <v>5</v>
-      </c>
-      <c r="B14" t="n">
-        <v>53.0</v>
-      </c>
     </row>
     <row r="15">
-      <c r="A15" t="s" s="2">
-        <v>11</v>
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+      <c r="B15" t="n">
+        <v>66.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B16" t="n">
-        <v>66.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5.0</v>
+      <c r="A17" t="s" s="2">
+        <v>11</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>12</v>
+      <c r="A18" t="s">
+        <v>8</v>
+      </c>
+      <c r="B18" t="n">
+        <v>19.0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B19" t="n">
-        <v>19.0</v>
+        <v>28.0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="B20" t="n">
-        <v>28.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B21" t="n">
-        <v>4.0</v>
+        <v>49.0</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="s">
-        <v>10</v>
-      </c>
-      <c r="B22" t="n">
-        <v>1.0</v>
+      <c r="A22" t="s" s="2">
+        <v>12</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B23" t="n">
-        <v>48.0</v>
+        <v>26.0</v>
       </c>
     </row>
     <row r="24">
@@ -369,52 +363,52 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B25" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="s">
-        <v>3</v>
-      </c>
-      <c r="B26" t="n">
-        <v>25.0</v>
+      <c r="A26" t="s" s="2">
+        <v>14</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="s" s="2">
-        <v>14</v>
+      <c r="A27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B27" t="n">
+        <v>5.0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B28" t="n">
-        <v>2.0</v>
+        <v>22.0</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="s" s="2">
-        <v>15</v>
+      <c r="A29" t="s">
+        <v>3</v>
+      </c>
+      <c r="B29" t="n">
+        <v>20.0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B30" t="n">
-        <v>3.0</v>
+        <v>27.0</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="s">
-        <v>9</v>
-      </c>
-      <c r="B31" t="n">
-        <v>20.0</v>
+      <c r="A31" t="s" s="2">
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -422,97 +416,94 @@
         <v>3</v>
       </c>
       <c r="B32" t="n">
-        <v>23.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s">
-        <v>5</v>
-      </c>
-      <c r="B33" t="n">
-        <v>26.0</v>
+      <c r="A33" t="s" s="2">
+        <v>16</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="s" s="2">
-        <v>16</v>
+      <c r="A34" t="s">
+        <v>3</v>
+      </c>
+      <c r="B34" t="n">
+        <v>12.0</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="s">
-        <v>3</v>
-      </c>
-      <c r="B35" t="n">
-        <v>3.0</v>
+      <c r="A35" t="s" s="2">
+        <v>17</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="s" s="2">
-        <v>17</v>
+      <c r="A36" t="s">
+        <v>8</v>
+      </c>
+      <c r="B36" t="n">
+        <v>74.0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B37" t="n">
-        <v>12.0</v>
+        <v>55.0</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="s" s="2">
-        <v>18</v>
+      <c r="A38" t="s">
+        <v>3</v>
+      </c>
+      <c r="B38" t="n">
+        <v>23.0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B39" t="n">
-        <v>76.0</v>
+        <v>475.0</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="s">
-        <v>9</v>
-      </c>
-      <c r="B40" t="n">
-        <v>54.0</v>
+      <c r="A40" t="s" s="2">
+        <v>18</v>
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="s">
-        <v>3</v>
-      </c>
+      <c r="A41"/>
       <c r="B41" t="n">
-        <v>23.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B42" t="n">
-        <v>17.0</v>
+        <v>21.0</v>
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="s">
-        <v>5</v>
-      </c>
-      <c r="B43" t="n">
-        <v>458.0</v>
+      <c r="A43" t="s" s="2">
+        <v>19</v>
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>19</v>
+      <c r="A44" t="s">
+        <v>3</v>
+      </c>
+      <c r="B44" t="n">
+        <v>22.0</v>
       </c>
     </row>
     <row r="45">
-      <c r="A45"/>
-      <c r="B45" t="n">
-        <v>1.0</v>
+      <c r="A45" t="s" s="2">
+        <v>20</v>
       </c>
     </row>
     <row r="46">
@@ -520,25 +511,28 @@
         <v>3</v>
       </c>
       <c r="B46" t="n">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B48" t="n">
-        <v>22.0</v>
+        <v>9.0</v>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="s" s="2">
-        <v>21</v>
+      <c r="A49" t="s">
+        <v>9</v>
+      </c>
+      <c r="B49" t="n">
+        <v>21.0</v>
       </c>
     </row>
     <row r="50">
@@ -546,28 +540,28 @@
         <v>3</v>
       </c>
       <c r="B50" t="n">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="s" s="2">
+      <c r="A51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="n">
+        <v>23.0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="s" s="2">
         <v>22</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s">
-        <v>8</v>
-      </c>
-      <c r="B52" t="n">
-        <v>9.0</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B53" t="n">
-        <v>21.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="54">
@@ -575,44 +569,44 @@
         <v>3</v>
       </c>
       <c r="B54" t="n">
-        <v>2.0</v>
+        <v>11.0</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="s">
-        <v>10</v>
-      </c>
-      <c r="B55" t="n">
-        <v>1.0</v>
+      <c r="A55" t="s" s="2">
+        <v>23</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B56" t="n">
-        <v>22.0</v>
+        <v>12.0</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="s" s="2">
-        <v>23</v>
+      <c r="A57" t="s">
+        <v>9</v>
+      </c>
+      <c r="B57" t="n">
+        <v>4.0</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="B58" t="n">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B59" t="n">
-        <v>10.0</v>
+        <v>87.0</v>
       </c>
     </row>
     <row r="60">
@@ -625,7 +619,7 @@
         <v>8</v>
       </c>
       <c r="B61" t="n">
-        <v>12.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="62">
@@ -633,7 +627,7 @@
         <v>9</v>
       </c>
       <c r="B62" t="n">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="63">
@@ -641,28 +635,25 @@
         <v>3</v>
       </c>
       <c r="B63" t="n">
-        <v>5.0</v>
+        <v>67.0</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" t="n">
-        <v>3.0</v>
+      <c r="A64" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B65" t="n">
-        <v>84.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="67">
@@ -670,149 +661,83 @@
         <v>8</v>
       </c>
       <c r="B67" t="n">
-        <v>5.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B68" t="n">
-        <v>65.0</v>
+        <v>25.0</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B69" t="n">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="B71" t="n">
-        <v>7.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="s" s="2">
-        <v>27</v>
+      <c r="A72" t="s">
+        <v>3</v>
+      </c>
+      <c r="B72" t="n">
+        <v>5.0</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B73" t="n">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="s" s="2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75"/>
+      <c r="B75" t="n">
         <v>5.0</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="s">
-        <v>9</v>
-      </c>
-      <c r="B74" t="n">
-        <v>23.0</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" t="n">
-        <v>1.0</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="B76" t="n">
         <v>2.0</v>
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="s">
-        <v>5</v>
-      </c>
-      <c r="B77" t="n">
-        <v>4.0</v>
+      <c r="A77" t="s" s="2">
+        <v>29</v>
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="s" s="2">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s">
-        <v>8</v>
-      </c>
-      <c r="B79" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s">
-        <v>3</v>
-      </c>
-      <c r="B80" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="s">
-        <v>10</v>
-      </c>
-      <c r="B81" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83"/>
-      <c r="B83" t="n">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
-        <v>9</v>
-      </c>
-      <c r="B84" t="n">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="s">
-        <v>3</v>
-      </c>
-      <c r="B85" t="n">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="s">
-        <v>3</v>
-      </c>
-      <c r="B87" t="n">
+      <c r="A78" t="s">
+        <v>3</v>
+      </c>
+      <c r="B78" t="n">
         <v>35.0</v>
       </c>
     </row>
@@ -822,26 +747,26 @@
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A14:B14"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A22:B22"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="A29:B29"/>
-    <mergeCell ref="A34:B34"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A44:B44"/>
+    <mergeCell ref="A26:B26"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="A33:B33"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A45:B45"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A51:B51"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A52:B52"/>
+    <mergeCell ref="A55:B55"/>
     <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A64:B64"/>
     <mergeCell ref="A66:B66"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="A72:B72"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A86:B86"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A77:B77"/>
   </mergeCells>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
